--- a/Model/mini/data_my/11_花卉词频统计.xlsx
+++ b/Model/mini/data_my/11_花卉词频统计.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>157</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -457,216 +457,136 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>花毛茛</t>
+          <t>月季</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>虞美人</t>
+          <t>玉兰</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>月季</t>
+          <t>杜鹃</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>仙客来</t>
+          <t>绣球</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>玉兰</t>
+          <t>玫瑰</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>杜鹃</t>
+          <t>樱花</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>绣球</t>
+          <t>芍药</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>玫瑰</t>
+          <t>紫藤</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>樱花</t>
+          <t>鸢尾</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>芍药</t>
+          <t>海棠</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>迷迭香</t>
+          <t>向日葵</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>大丽花</t>
+          <t>桃花</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>紫藤</t>
+          <t>茶花</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>鸢尾</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>海棠</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>雏菊</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>天竺葵</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>向日葵</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>水仙</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>桃花</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>茶花</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
         <v>1</v>
       </c>
     </row>
